--- a/results/skill/2020_2023/compare_results-2020_2023.xlsx
+++ b/results/skill/2020_2023/compare_results-2020_2023.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\casadje\GitHub\EFAS_skill\results\skill\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\casadje\GitHub\EFAS_skill\results\skill\2020_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE5F0C9-0337-400E-ABBB-65733842A74E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072F6E7D-420F-49C4-9693-7135C796940E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12810" activeTab="1" xr2:uid="{732E8501-5F93-46DB-BB39-E0B4281FE1D0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12810" activeTab="2" xr2:uid="{732E8501-5F93-46DB-BB39-E0B4281FE1D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="34" r:id="rId1"/>
@@ -554,18 +554,25 @@
   </cellStyles>
   <dxfs count="46">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4"/>
-      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="7"/>
-      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -594,106 +601,6 @@
         <i val="0"/>
         <color theme="7"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="4"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="7"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.000"/>
@@ -950,6 +857,99 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="4"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="7"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1064,12 +1064,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EDE5198D-7F12-47EF-8CE9-45F248B249B5}" name="skill_by_criteria__46" displayName="skill_by_criteria__46" ref="A1:M6" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:M6" xr:uid="{C36B3B4E-2401-4A27-8EDF-3273332DA90F}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{970F2EBD-5213-4B3A-B49C-26F851A01621}" uniqueName="1" name="approach" queryTableFieldId="1" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{970F2EBD-5213-4B3A-B49C-26F851A01621}" uniqueName="1" name="approach" queryTableFieldId="1" dataDxfId="45"/>
     <tableColumn id="2" xr3:uid="{CD8D43CF-242E-4114-991E-7B5A3B7289C6}" uniqueName="2" name="window" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F951C973-B398-46DA-8F61-8B4A3EE0790E}" uniqueName="3" name="KGE" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{B39429FB-BFE7-430B-B161-99AB8C51D18E}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{B39429FB-BFE7-430B-B161-99AB8C51D18E}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="44"/>
     <tableColumn id="5" xr3:uid="{255A88C2-387F-4467-96EB-AF205B413041}" uniqueName="5" name="probability" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{4A0CB78D-6CA4-43C6-AD69-663272A42255}" uniqueName="6" name="persistencee" queryTableFieldId="6" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{4A0CB78D-6CA4-43C6-AD69-663272A42255}" uniqueName="6" name="persistencee" queryTableFieldId="6" dataDxfId="43"/>
     <tableColumn id="7" xr3:uid="{C300F2BC-7037-4065-8AEF-791D4B4D9B9B}" uniqueName="7" name="TP" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{09B0C3EB-C26A-48D0-ACEF-04BA56C8D2A0}" uniqueName="8" name="FN" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{AFAF03A4-55F9-4B22-8001-082DDAF3601B}" uniqueName="9" name="FP" queryTableFieldId="9"/>
@@ -1105,23 +1105,23 @@
     <sortCondition ref="A1:A66"/>
   </sortState>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{69C7BAED-ECE0-461B-BC7A-751D89958422}" uniqueName="1" name="approach/model" queryTableFieldId="1" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{69C7BAED-ECE0-461B-BC7A-751D89958422}" uniqueName="1" name="approach/model" queryTableFieldId="1" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{D1B0C460-FC1C-479D-920B-C8214A32D3AB}" uniqueName="2" name="window" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A0F9CFB4-665C-49D4-9DD1-17D3BDA034AA}" uniqueName="3" name="KGE" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{B470D862-39D2-48AD-BF4B-4A1EE3DF0851}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{B470D862-39D2-48AD-BF4B-4A1EE3DF0851}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="29"/>
     <tableColumn id="5" xr3:uid="{502EE63F-66C0-43C8-B661-B186C0581205}" uniqueName="5" name="min_leadtime" queryTableFieldId="5"/>
     <tableColumn id="18" xr3:uid="{BD3A52E7-BA83-4782-AA69-5A4EABD016E9}" uniqueName="18" name="max_leadtime" queryTableFieldId="18"/>
-    <tableColumn id="6" xr3:uid="{0C5C8495-906E-4A3B-ABD4-0F926B44D58A}" uniqueName="6" name="probability" queryTableFieldId="6" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{CD148422-D208-4450-8DC2-C164E6CF343F}" uniqueName="7" name="persistence" queryTableFieldId="7" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{32B840C2-7572-4E8A-88F0-8F3818C1E414}" uniqueName="8" name="TP" queryTableFieldId="8" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{9FADC3B6-AFD0-46D2-9DA7-6E84D0DC8F05}" uniqueName="9" name="FN" queryTableFieldId="9" dataDxfId="40"/>
-    <tableColumn id="10" xr3:uid="{3D505E5F-EDA6-4E0A-B27D-47D78CEFCB83}" uniqueName="10" name="FP" queryTableFieldId="10" dataDxfId="39"/>
-    <tableColumn id="11" xr3:uid="{244087C9-9921-49AA-9A70-141E04F4FC14}" uniqueName="11" name="no_events" queryTableFieldId="11" dataDxfId="38"/>
-    <tableColumn id="12" xr3:uid="{73F125C8-B472-4593-90D7-4D9FF1BEE6D5}" uniqueName="12" name="recall" queryTableFieldId="12" dataDxfId="37"/>
-    <tableColumn id="13" xr3:uid="{39B1F2F9-C9AD-4489-B5C6-73F7A9EC3A8D}" uniqueName="13" name="precision" queryTableFieldId="13" dataDxfId="36"/>
-    <tableColumn id="14" xr3:uid="{3E7158C1-A8A4-4EA0-B3E9-44C2BD8D5732}" uniqueName="14" name="f0.8" queryTableFieldId="14" dataDxfId="35"/>
-    <tableColumn id="15" xr3:uid="{A369D44C-D73D-4C7A-B5C0-6FD6794C9B9C}" uniqueName="15" name="f1" queryTableFieldId="15" dataDxfId="34"/>
-    <tableColumn id="16" xr3:uid="{101B5045-0F59-439A-BFCA-AB649BB2B3F8}" uniqueName="16" name="f1.25" queryTableFieldId="16" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{0C5C8495-906E-4A3B-ABD4-0F926B44D58A}" uniqueName="6" name="probability" queryTableFieldId="6" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{CD148422-D208-4450-8DC2-C164E6CF343F}" uniqueName="7" name="persistence" queryTableFieldId="7" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{32B840C2-7572-4E8A-88F0-8F3818C1E414}" uniqueName="8" name="TP" queryTableFieldId="8" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{9FADC3B6-AFD0-46D2-9DA7-6E84D0DC8F05}" uniqueName="9" name="FN" queryTableFieldId="9" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{3D505E5F-EDA6-4E0A-B27D-47D78CEFCB83}" uniqueName="10" name="FP" queryTableFieldId="10" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{244087C9-9921-49AA-9A70-141E04F4FC14}" uniqueName="11" name="no_events" queryTableFieldId="11" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{73F125C8-B472-4593-90D7-4D9FF1BEE6D5}" uniqueName="12" name="recall" queryTableFieldId="12" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{39B1F2F9-C9AD-4489-B5C6-73F7A9EC3A8D}" uniqueName="13" name="precision" queryTableFieldId="13" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{3E7158C1-A8A4-4EA0-B3E9-44C2BD8D5732}" uniqueName="14" name="f0.8" queryTableFieldId="14" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{A369D44C-D73D-4C7A-B5C0-6FD6794C9B9C}" uniqueName="15" name="f1" queryTableFieldId="15" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{101B5045-0F59-439A-BFCA-AB649BB2B3F8}" uniqueName="16" name="f1.25" queryTableFieldId="16" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1131,20 +1131,20 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{317230A8-31E7-401E-941B-10842BF0D400}" name="skill_by_criteria__36" displayName="skill_by_criteria__36" ref="A1:N92" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N92" xr:uid="{8147D1A5-FBD1-4E91-BA4C-3427A2467CD0}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{5AE7C3FF-A8A0-4649-9C29-4F78B6EA4679}" uniqueName="1" name="approach" queryTableFieldId="1" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{5AE7C3FF-A8A0-4649-9C29-4F78B6EA4679}" uniqueName="1" name="approach" queryTableFieldId="1" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{2F53DF83-F290-437E-A129-BF5D583AFDDE}" uniqueName="2" name="window" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{ED00E885-F599-46E4-90EE-87AE82FEB197}" uniqueName="3" name="KGE" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{C332DA5D-DE3A-4B32-962A-9A93F11293A5}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{C332DA5D-DE3A-4B32-962A-9A93F11293A5}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="16"/>
     <tableColumn id="5" xr3:uid="{4DB69A4D-7413-4286-A18C-EADB8A9C53CC}" uniqueName="5" name="leadtime" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{70307283-1139-4219-839C-DB88D129A7D0}" uniqueName="6" name="probability" queryTableFieldId="6" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{4F1716B9-F364-4444-9481-81D533533DAC}" uniqueName="7" name="persistence" queryTableFieldId="7" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{70307283-1139-4219-839C-DB88D129A7D0}" uniqueName="6" name="probability" queryTableFieldId="6" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{4F1716B9-F364-4444-9481-81D533533DAC}" uniqueName="7" name="persistence" queryTableFieldId="7" dataDxfId="14"/>
     <tableColumn id="8" xr3:uid="{FC85DB4E-6F8D-4230-A9F5-90F4EA3C2B4E}" uniqueName="8" name="TP" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{9ABCCEED-8A94-4D77-B351-C535F070C806}" uniqueName="9" name="FN" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{28AF3861-1CA4-4DC4-9D30-8723F4D254F2}" uniqueName="10" name="FP" queryTableFieldId="10"/>
     <tableColumn id="11" xr3:uid="{A6CE56A0-39E8-4397-BBDD-C33EE1D594CE}" uniqueName="11" name="no_events" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{278B3752-75A7-4E38-9E73-CAF0A406A305}" uniqueName="12" name="recall" queryTableFieldId="12" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{368211AF-DA66-44D2-B49F-33574A8DD598}" uniqueName="13" name="precision" queryTableFieldId="13" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{B27D3CB5-6BD2-41DE-BE63-8293FA51734A}" uniqueName="14" name="f0.8" queryTableFieldId="14" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{278B3752-75A7-4E38-9E73-CAF0A406A305}" uniqueName="12" name="recall" queryTableFieldId="12" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{368211AF-DA66-44D2-B49F-33574A8DD598}" uniqueName="13" name="precision" queryTableFieldId="13" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{B27D3CB5-6BD2-41DE-BE63-8293FA51734A}" uniqueName="14" name="f0.8" queryTableFieldId="14" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1154,20 +1154,20 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{AF1F94BE-1630-4B7C-B953-EFA1D0B14028}" name="skill_by_criteria__41" displayName="skill_by_criteria__41" ref="A1:N48" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N48" xr:uid="{3119605B-0323-4D51-BA96-A5CBF1032DD3}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{8F960F8B-6210-428C-93EA-0F714094BCC7}" uniqueName="1" name="approach" queryTableFieldId="1" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{8F960F8B-6210-428C-93EA-0F714094BCC7}" uniqueName="1" name="approach" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{CB522D39-2F4B-497D-801F-005E1E30A268}" uniqueName="2" name="window" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{FCD8DA12-110B-47FB-A8B9-BEA58A9663C8}" uniqueName="3" name="KGE" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{73E97702-2DF3-4207-A2DF-79ADCCF9AD22}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{73E97702-2DF3-4207-A2DF-79ADCCF9AD22}" uniqueName="4" name="OF" queryTableFieldId="4" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{11907AE8-4EA3-4658-B1CF-A623C2FA9947}" uniqueName="5" name="leadtime" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{E96385A0-580B-4C48-A61A-4402D1460303}" uniqueName="6" name="probability" queryTableFieldId="6" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{5D987B15-AD9C-4C3E-8F31-5DA6692D9977}" uniqueName="7" name="persistence" queryTableFieldId="7" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{E96385A0-580B-4C48-A61A-4402D1460303}" uniqueName="6" name="probability" queryTableFieldId="6" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5D987B15-AD9C-4C3E-8F31-5DA6692D9977}" uniqueName="7" name="persistence" queryTableFieldId="7" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{9E1872A5-8F49-4F51-9788-41D01E89A30A}" uniqueName="8" name="TP" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{7D9BE3E4-4228-414D-9BEA-5744A15E8E70}" uniqueName="9" name="FN" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{0AF572A0-1E1C-4671-86D6-84FA4A7AD74B}" uniqueName="10" name="FP" queryTableFieldId="10"/>
     <tableColumn id="11" xr3:uid="{A572C04F-B17F-473E-B9C5-5D97DA6F421C}" uniqueName="11" name="no_events" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{C886C0CD-A2D0-4D4C-B7A9-4144B470306F}" uniqueName="12" name="recall" queryTableFieldId="12" dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{010A2B21-877D-4AA0-B109-6B11A137CD51}" uniqueName="13" name="precision" queryTableFieldId="13" dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{26D6D895-EEBC-4CD5-BE62-33E53E1E71B1}" uniqueName="14" name="f0.8" queryTableFieldId="14" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{C886C0CD-A2D0-4D4C-B7A9-4144B470306F}" uniqueName="12" name="recall" queryTableFieldId="12" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{010A2B21-877D-4AA0-B109-6B11A137CD51}" uniqueName="13" name="precision" queryTableFieldId="13" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{26D6D895-EEBC-4CD5-BE62-33E53E1E71B1}" uniqueName="14" name="f0.8" queryTableFieldId="14" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1471,24 +1471,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B82AD64-BBFB-46C0-83D9-F2DD47FCCBFA}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
         <v>3</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>0.51500000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>0.55200000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>15</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>0.55700000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>16</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
         <v>2</v>
       </c>
@@ -1745,13 +1745,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24CE5352-E4DB-4452-A238-93008838F217}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>25</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>0.51500000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>0.55200000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>15</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>0.54600000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
         <v>48</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>0.55700000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>16</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>2</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>0.55600000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>0.52700000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="48" t="s">
         <v>20</v>
       </c>
@@ -2181,17 +2181,17 @@
         <v>0.55300000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="29" t="s">
         <v>26</v>
       </c>
@@ -2202,26 +2202,26 @@
     <sortCondition ref="A2:A7"/>
   </sortState>
   <conditionalFormatting sqref="L4:M7">
-    <cfRule type="expression" dxfId="15" priority="721">
+    <cfRule type="expression" dxfId="42" priority="721">
       <formula>L4=MIN(L$2:L$3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="722">
+    <cfRule type="expression" dxfId="41" priority="722">
       <formula>L4=MAX(L$2:L$3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G7 K2:M7">
-    <cfRule type="expression" dxfId="13" priority="891">
+    <cfRule type="expression" dxfId="40" priority="891">
       <formula>G2=MIN(G$2:G$9)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="892">
+    <cfRule type="expression" dxfId="39" priority="892">
       <formula>G2=MAX(G$2:G$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I7">
-    <cfRule type="expression" dxfId="11" priority="911">
+    <cfRule type="expression" dxfId="38" priority="911">
       <formula>H2=MAX(H$2:H$9)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="912">
+    <cfRule type="expression" dxfId="37" priority="912">
       <formula>H2=MIN(H$2:H$9)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2233,21 +2233,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981285E5-5B1F-4ECD-8D9D-A8A24790817E}">
   <dimension ref="A1:Q72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.1796875" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7265625" customWidth="1"/>
+    <col min="5" max="6" width="9.1796875" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1796875" customWidth="1"/>
     <col min="16" max="17" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -2349,7 +2349,7 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>3</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>0.56299999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
@@ -2449,7 +2449,7 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>0.66800000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
         <v>15</v>
       </c>
@@ -2547,7 +2547,7 @@
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>15</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>0.67400000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>48</v>
       </c>
@@ -2645,7 +2645,7 @@
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>21</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>0.66600000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="30" t="s">
         <v>3</v>
       </c>
@@ -2745,7 +2745,7 @@
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
         <v>3</v>
       </c>
@@ -2792,7 +2792,7 @@
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
         <v>15</v>
       </c>
@@ -2839,7 +2839,7 @@
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
         <v>20</v>
       </c>
@@ -2886,7 +2886,7 @@
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>16</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>0.67500000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
         <v>2</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>0.67600000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="s">
         <v>3</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>0.441</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
         <v>3</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>0.48899999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
         <v>15</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>0.47299999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
         <v>3</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>0.48699999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
         <v>48</v>
       </c>
@@ -3241,7 +3241,7 @@
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
         <v>48</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="30" t="s">
         <v>3</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>0.439</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>16</v>
       </c>
@@ -3388,7 +3388,7 @@
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
         <v>21</v>
       </c>
@@ -3435,7 +3435,7 @@
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
         <v>22</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>0.55400000000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
         <v>21</v>
       </c>
@@ -3533,7 +3533,7 @@
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
         <v>21</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>0.45700000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
         <v>15</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
         <v>22</v>
       </c>
@@ -3680,7 +3680,7 @@
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
         <v>19</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
         <v>22</v>
       </c>
@@ -3777,7 +3777,7 @@
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
         <v>22</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
         <v>16</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>0.46200000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
         <v>21</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>0.45700000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
         <v>22</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>0.27400000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
         <v>19</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="47" t="s">
         <v>20</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>0.68100000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="21" t="s">
         <v>19</v>
       </c>
@@ -4121,7 +4121,7 @@
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
         <v>19</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="21" t="s">
         <v>22</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>0.42899999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
         <v>19</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>0.22800000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
         <v>19</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>0.221</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="21" t="s">
         <v>20</v>
       </c>
@@ -4371,7 +4371,7 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="21" t="s">
         <v>19</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>0.41599999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="47" t="s">
         <v>20</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="21" t="s">
         <v>16</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>0.42599999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="21" t="s">
         <v>2</v>
       </c>
@@ -4571,7 +4571,7 @@
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="30" t="s">
         <v>3</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>0.216</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="21" t="s">
         <v>3</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>0.26100000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="21" t="s">
         <v>15</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="21" t="s">
         <v>48</v>
       </c>
@@ -4773,7 +4773,7 @@
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
         <v>16</v>
       </c>
@@ -4820,7 +4820,7 @@
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="47" t="s">
         <v>20</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>0.316</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="21" t="s">
         <v>16</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="21" t="s">
         <v>2</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0.49399999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="21" t="s">
         <v>2</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>0.32400000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="30" t="s">
         <v>3</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="21" t="s">
         <v>3</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>0.252</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="21" t="s">
         <v>2</v>
       </c>
@@ -5175,7 +5175,7 @@
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="21" t="s">
         <v>15</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="21" t="s">
         <v>48</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="21" t="s">
         <v>2</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>0.45400000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="47" t="s">
         <v>20</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>0.27100000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="21" t="s">
         <v>16</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>0.24199999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="21" t="s">
         <v>2</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>0.26100000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="47" t="s">
         <v>20</v>
       </c>
@@ -5534,48 +5534,48 @@
         <v>0.45800000000000002</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" s="23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71" s="33" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" s="29" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q2:Q66">
-    <cfRule type="expression" dxfId="9" priority="191">
+    <cfRule type="expression" dxfId="36" priority="191">
       <formula>Q2=MIN(Q$2:Q$2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="192">
+    <cfRule type="expression" dxfId="35" priority="192">
       <formula>Q2=MAX(Q$2:Q$2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:P66 I2:I66">
-    <cfRule type="expression" dxfId="3" priority="933">
+    <cfRule type="expression" dxfId="34" priority="933">
       <formula>I2=MIN(I$2:I$66)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="934">
+    <cfRule type="expression" dxfId="33" priority="934">
       <formula>I2=MAX(I$2:I$66)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K66">
-    <cfRule type="expression" dxfId="1" priority="941">
+    <cfRule type="expression" dxfId="32" priority="941">
       <formula>J2=MAX(J$2:J$66)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="942">
+    <cfRule type="expression" dxfId="31" priority="942">
       <formula>J2=MIN(J$2:J$66)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5590,25 +5590,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78C1BC26-F995-446C-BC9C-609D1D53BFF1}">
   <dimension ref="A1:N92"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>0.70199999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>15</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>0.74399999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>16</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>0.74399999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
         <v>2</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>0.70599999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>21</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>0.70199999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>22</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>0.64700000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>19</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>0.67900000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="47" t="s">
         <v>20</v>
       </c>
@@ -6028,7 +6028,7 @@
         <v>0.70499999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="30" t="s">
         <v>3</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>0.57699999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
         <v>3</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>0.64500000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
         <v>15</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>0.65500000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>16</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
         <v>2</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>0.65300000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
         <v>21</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>0.63900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
         <v>22</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>0.49399999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
         <v>19</v>
       </c>
@@ -6362,7 +6362,7 @@
         <v>0.54700000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="47" t="s">
         <v>20</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>0.66100000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="30" t="s">
         <v>3</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>0.53300000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
         <v>3</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>0.56299999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
         <v>15</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>0.56899999999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>16</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>0.56299999999999994</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
         <v>2</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
         <v>21</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>0.53600000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="21" t="s">
         <v>22</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="21" t="s">
         <v>19</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>0.47299999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="47" t="s">
         <v>20</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>0.57199999999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="30" t="s">
         <v>3</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>0.496</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
         <v>3</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>0.51400000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
         <v>15</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>0.502</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
         <v>16</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>0.498</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
         <v>2</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>0.52300000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
         <v>21</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>0.495</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
         <v>22</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>0.36199999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
         <v>19</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="47" t="s">
         <v>20</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>0.51500000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="30" t="s">
         <v>3</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>0.42399999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
         <v>3</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>0.46800000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="21" t="s">
         <v>15</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
         <v>16</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
         <v>2</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>0.49399999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="21" t="s">
         <v>21</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>0.41499999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="21" t="s">
         <v>22</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>0.29099999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="21" t="s">
         <v>19</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>0.36199999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="47" t="s">
         <v>20</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>0.48499999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="30" t="s">
         <v>3</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>0.36899999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="21" t="s">
         <v>3</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="21" t="s">
         <v>15</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="21" t="s">
         <v>16</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>0.39500000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="21" t="s">
         <v>2</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>0.42799999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
         <v>21</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>0.34300000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="21" t="s">
         <v>22</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>0.26900000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="21" t="s">
         <v>19</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>0.32100000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="47" t="s">
         <v>20</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="30" t="s">
         <v>3</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>0.35499999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="21" t="s">
         <v>3</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>0.39600000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="21" t="s">
         <v>15</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>0.39200000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="21" t="s">
         <v>16</v>
       </c>
@@ -8078,7 +8078,7 @@
         <v>0.35699999999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="21" t="s">
         <v>2</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="21" t="s">
         <v>22</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>0.25600000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="21" t="s">
         <v>19</v>
       </c>
@@ -8200,7 +8200,7 @@
         <v>0.307</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="47" t="s">
         <v>20</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>0.39700000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="30" t="s">
         <v>3</v>
       </c>
@@ -8286,7 +8286,7 @@
         <v>0.31900000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="21" t="s">
         <v>3</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>0.38700000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="21" t="s">
         <v>15</v>
       </c>
@@ -8370,7 +8370,7 @@
         <v>0.379</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="21" t="s">
         <v>16</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>0.33400000000000002</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="21" t="s">
         <v>2</v>
       </c>
@@ -8456,7 +8456,7 @@
         <v>0.38600000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="21" t="s">
         <v>22</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>0.20399999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="21" t="s">
         <v>19</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>0.248</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="47" t="s">
         <v>20</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>0.377</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="30" t="s">
         <v>3</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="21" t="s">
         <v>3</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>0.33100000000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="21" t="s">
         <v>15</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>0.34399999999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="21" t="s">
         <v>16</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>0.30199999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="21" t="s">
         <v>2</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>0.33700000000000002</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="21" t="s">
         <v>19</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>0.20499999999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="47" t="s">
         <v>20</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>0.33600000000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="30" t="s">
         <v>3</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>0.191</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="21" t="s">
         <v>3</v>
       </c>
@@ -8960,7 +8960,7 @@
         <v>0.27900000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="21" t="s">
         <v>15</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>0.29099999999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="21" t="s">
         <v>16</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>0.25700000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="21" t="s">
         <v>2</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>0.307</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="21" t="s">
         <v>19</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>0.161</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="47" t="s">
         <v>20</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>0.30399999999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="30" t="s">
         <v>3</v>
       </c>
@@ -9200,7 +9200,7 @@
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="21" t="s">
         <v>3</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>0.24099999999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="21" t="s">
         <v>15</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>0.27300000000000002</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="21" t="s">
         <v>16</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>0.21199999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="21" t="s">
         <v>2</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="21" t="s">
         <v>19</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="47" t="s">
         <v>20</v>
       </c>
@@ -9461,25 +9461,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3912CC-F663-492D-A714-E0315EE02060}">
   <dimension ref="A1:N48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -9523,7 +9523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="44" t="s">
         <v>3</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>0.63400000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="44" t="s">
         <v>20</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>0.69899999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>0.69399999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>45</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>0.73799999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
         <v>46</v>
       </c>
@@ -9735,7 +9735,7 @@
         <v>0.73699999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>47</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>0.73599999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>48</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>49</v>
       </c>
@@ -9861,7 +9861,7 @@
         <v>0.73199999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
         <v>50</v>
       </c>
@@ -9903,7 +9903,7 @@
         <v>0.73199999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
         <v>2</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="44" t="s">
         <v>3</v>
       </c>
@@ -9989,7 +9989,7 @@
         <v>0.51800000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="44" t="s">
         <v>20</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>0.56200000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>3</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>0.55400000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
         <v>42</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>0.55600000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
         <v>43</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>0.56200000000000006</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
         <v>44</v>
       </c>
@@ -10199,7 +10199,7 @@
         <v>0.56599999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
         <v>45</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>0.56899999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
         <v>46</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>0.57099999999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
         <v>47</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>0.57099999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
         <v>48</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>0.57599999999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
         <v>49</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>0.57199999999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>50</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>0.57499999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
         <v>16</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>0.55900000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="21" t="s">
         <v>2</v>
       </c>
@@ -10535,7 +10535,7 @@
         <v>0.57399999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="44" t="s">
         <v>3</v>
       </c>
@@ -10579,7 +10579,7 @@
         <v>0.35599999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="44" t="s">
         <v>20</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>0.40200000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="21" t="s">
         <v>3</v>
       </c>
@@ -10663,7 +10663,7 @@
         <v>0.39900000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="21" t="s">
         <v>42</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>0.38300000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="21" t="s">
         <v>43</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>0.39500000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="21" t="s">
         <v>44</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>0.38900000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="21" t="s">
         <v>45</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>0.39800000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="21" t="s">
         <v>46</v>
       </c>
@@ -10873,7 +10873,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="21" t="s">
         <v>47</v>
       </c>
@@ -10915,7 +10915,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="21" t="s">
         <v>48</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="21" t="s">
         <v>49</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>0.40699999999999997</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="21" t="s">
         <v>50</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>0.40500000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="21" t="s">
         <v>2</v>
       </c>
@@ -11083,7 +11083,7 @@
         <v>0.40100000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="44" t="s">
         <v>3</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>0.23699999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="44" t="s">
         <v>20</v>
       </c>
@@ -11171,7 +11171,7 @@
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
         <v>3</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>0.33400000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
         <v>45</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>0.34699999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="21" t="s">
         <v>46</v>
       </c>
@@ -11297,7 +11297,7 @@
         <v>0.33800000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="21" t="s">
         <v>47</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>0.34399999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="21" t="s">
         <v>48</v>
       </c>
@@ -11381,7 +11381,7 @@
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="21" t="s">
         <v>49</v>
       </c>
@@ -11423,7 +11423,7 @@
         <v>0.34100000000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="21" t="s">
         <v>50</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>0.33100000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="21" t="s">
         <v>2</v>
       </c>
@@ -11511,18 +11511,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H24 L24:N24">
-    <cfRule type="expression" dxfId="7" priority="927">
+    <cfRule type="expression" dxfId="10" priority="927">
       <formula>H24=MIN(H$2:H$61)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="928">
+    <cfRule type="expression" dxfId="9" priority="928">
       <formula>H24=MAX(H$2:H$61)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:J24">
-    <cfRule type="expression" dxfId="5" priority="931">
+    <cfRule type="expression" dxfId="8" priority="931">
       <formula>I24=MAX(I$2:I$61)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="932">
+    <cfRule type="expression" dxfId="7" priority="932">
       <formula>I24=MIN(I$2:I$61)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11537,13 +11537,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{515ACACE-37C4-4B6C-9E7F-01A399C0AB1F}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -11599,7 +11599,7 @@
         <v>0.27675097276264587</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>0.18968871595330741</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -11659,7 +11659,7 @@
         <v>0.2310311284046693</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -11689,7 +11689,7 @@
         <v>0.30252918287937747</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B6" s="35"/>
       <c r="D6" s="1">
         <f>+SUM(D2:D5)</f>
@@ -11701,7 +11701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>7.85E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>2.0699999999999998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>37</v>
       </c>
